--- a/Result/profitability/3491.xlsx
+++ b/Result/profitability/3491.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>2.20375</v>
+        <v>2.50375</v>
       </c>
       <c r="N2" t="n">
-        <v>51.47875000000001</v>
+        <v>51.97375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.71</v>
       </c>
       <c r="M3" t="n">
-        <v>2.15875</v>
+        <v>2.40625</v>
       </c>
       <c r="N3" t="n">
-        <v>51.06874999999999</v>
+        <v>51.6575</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>2.14</v>
       </c>
       <c r="M4" t="n">
-        <v>2.115</v>
+        <v>2.39625</v>
       </c>
       <c r="N4" t="n">
-        <v>50.99625</v>
+        <v>51.625</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>2.17</v>
       </c>
       <c r="M5" t="n">
-        <v>2.10875</v>
+        <v>2.53375</v>
       </c>
       <c r="N5" t="n">
-        <v>50.8675</v>
+        <v>52.39875</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.91</v>
       </c>
       <c r="M6" t="n">
-        <v>2.08875</v>
+        <v>2.48125</v>
       </c>
       <c r="N6" t="n">
-        <v>51.66249999999999</v>
+        <v>52.69875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.87</v>
       </c>
       <c r="M7" t="n">
-        <v>2.03125</v>
+        <v>2.18125</v>
       </c>
       <c r="N7" t="n">
-        <v>52.11</v>
+        <v>51.73875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.91</v>
       </c>
       <c r="M8" t="n">
-        <v>1.73625</v>
+        <v>1.835</v>
       </c>
       <c r="N8" t="n">
-        <v>51.11125</v>
+        <v>50.81375000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>0.22</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6925</v>
+        <v>0.6925000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>47.775</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3491</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>902</v>
+      </c>
+      <c r="D75" t="n">
+        <v>401</v>
+      </c>
+      <c r="E75" t="n">
+        <v>502</v>
+      </c>
+      <c r="F75" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="G75" t="n">
+        <v>241</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>26.77%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>114</v>
+      </c>
+      <c r="J75" t="n">
+        <v>356</v>
+      </c>
+      <c r="K75" t="n">
+        <v>308</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.575</v>
+      </c>
+      <c r="N75" t="n">
+        <v>51.98875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.7899999999999996</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.214673913043478</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.379999999999995</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04104863746119347</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>3.399999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3.177570093457944</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2825836216839677</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
